--- a/AAII_Financials/Yearly/LAD_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LAD_YR_FIN.xlsx
@@ -1008,13 +1008,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>37900</v>
+        <v>44600</v>
       </c>
       <c r="E14" s="3">
-        <v>-22800</v>
+        <v>-16700</v>
       </c>
       <c r="F14" s="3">
-        <v>43200</v>
+        <v>48600</v>
       </c>
       <c r="G14" s="3">
         <v>54200</v>
@@ -1128,13 +1128,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>36008000</v>
+        <v>36001300</v>
       </c>
       <c r="E17" s="3">
-        <v>34607000</v>
+        <v>34600900</v>
       </c>
       <c r="F17" s="3">
-        <v>29305800</v>
+        <v>29300400</v>
       </c>
       <c r="G17" s="3">
         <v>26231700</v>
@@ -1179,13 +1179,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1626900</v>
+        <v>1633600</v>
       </c>
       <c r="E18" s="3">
-        <v>1581200</v>
+        <v>1587300</v>
       </c>
       <c r="F18" s="3">
-        <v>1736500</v>
+        <v>1741900</v>
       </c>
       <c r="G18" s="3">
         <v>1956100</v>
@@ -1302,13 +1302,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1912400</v>
+        <v>1919100</v>
       </c>
       <c r="E21" s="3">
-        <v>1830700</v>
+        <v>1836800</v>
       </c>
       <c r="F21" s="3">
-        <v>1953400</v>
+        <v>1958800</v>
       </c>
       <c r="G21" s="3">
         <v>2115300</v>
@@ -2165,10 +2165,10 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>341800</v>
+        <v>109200</v>
       </c>
       <c r="E41" s="3">
-        <v>402200</v>
+        <v>225100</v>
       </c>
       <c r="F41" s="3">
         <v>941400</v>
